--- a/results/Int Task Remove ACC 0.7/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC 0.7/Rando_4_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7412147498848234</v>
+        <v>0.734355677602386</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7222272738294415</v>
+        <v>0.7379549477461749</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7236669818869572</v>
+        <v>0.7576759171698066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7318975655294488</v>
+        <v>0.7197555224170122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7318975655294488</v>
+        <v>0.7229744065371839</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7340434882762299</v>
+        <v>0.7143907155500594</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7333236342474722</v>
+        <v>0.7143907155500594</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7372623723964016</v>
+        <v>0.7161835309522078</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7372623723964016</v>
+        <v>0.7262069299968479</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.740834363861206</v>
+        <v>0.7258265439732305</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7311504328217066</v>
+        <v>0.7258265439732305</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7345723915520963</v>
+        <v>0.7386748017749327</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7278087946461046</v>
+        <v>0.7404403384980967</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7313671467714168</v>
+        <v>0.7404403384980967</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7547813462331175</v>
+        <v>0.6891685458645522</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7516033801314226</v>
+        <v>0.6863164084285056</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7641394486069688</v>
+        <v>0.6877561164860212</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7444048398438448</v>
+        <v>0.6891685458645522</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7444321185228293</v>
+        <v>0.6884077738173178</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7366091995829394</v>
+        <v>0.6873348124439271</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7294515773138381</v>
+        <v>0.6643131228631701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.730904924710846</v>
+        <v>0.6721905991610291</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.730904924710846</v>
+        <v>0.6478246768992022</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7379125142455324</v>
+        <v>0.6638645401420916</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7386187289347979</v>
+        <v>0.669365740403967</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7264357678038845</v>
+        <v>0.669365740403967</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7282285832060328</v>
+        <v>0.6710630804296696</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7206905749133143</v>
+        <v>0.6850388569627313</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7156925147304867</v>
+        <v>0.6767946339807474</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7156925147304867</v>
+        <v>0.6724755098082006</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7349921801120245</v>
+        <v>0.6777857593171843</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7353589267961494</v>
+        <v>0.5722687980407847</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7353589267961494</v>
+        <v>0.5680860672631605</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.744676111151524</v>
+        <v>0.5552105307824737</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7768649523532407</v>
+        <v>0.6037650638927281</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7768649523532407</v>
+        <v>0.6095238961227905</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7725731068596785</v>
+        <v>0.6298298416624233</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6234178366188987</v>
+        <v>0.6319484857302199</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6234178366188987</v>
+        <v>0.6533122378215853</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6701265124512015</v>
+        <v>0.6569524259838511</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6747305472709197</v>
+        <v>0.6244923134744551</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6875378870541451</v>
+        <v>0.6125533449722363</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6439950534662108</v>
+        <v>0.5964589243713779</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6404094226619141</v>
+        <v>0.5964589243713779</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6404094226619141</v>
+        <v>0.5711018767731142</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6456529909556025</v>
+        <v>0.5223563929099683</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.574443514948716</v>
+        <v>0.5188116801241484</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6026390606435343</v>
+        <v>0.4999878761426735</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6116576950122451</v>
+        <v>0.5000287941611503</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.590713731480808</v>
+        <v>0.4935773865813147</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5967574743580417</v>
+        <v>0.5009123202638152</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5967574743580417</v>
+        <v>0.5009123202638152</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6036029073009869</v>
+        <v>0.4977070754831358</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.614671989040033</v>
+        <v>0.5082336146068233</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6108560049465338</v>
+        <v>0.496581072233942</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6218159719696419</v>
+        <v>0.4986057564074586</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5189874760553818</v>
+        <v>0.4940699182852016</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5154427632695618</v>
+        <v>0.5033734633010838</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5028657767755389</v>
+        <v>0.4915587643364613</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4972160592614146</v>
+        <v>0.4877291409034699</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4972296986009068</v>
+        <v>0.4888430202953372</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5021595620862733</v>
+        <v>0.5113858175116995</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5014533473970079</v>
+        <v>0.6204505225382508</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5028657767755389</v>
+        <v>0.6303360127058024</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5114494677626633</v>
+        <v>0.6497857108217551</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5100233990446401</v>
+        <v>0.6504919255110206</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.507877476297859</v>
+        <v>0.5796764748672438</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5082305836424916</v>
+        <v>0.5850003637157197</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5082305836424916</v>
+        <v>0.569884944593972</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5032188841201717</v>
+        <v>0.5226503964501346</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5021459227467812</v>
+        <v>0.5131407458597027</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5021459227467812</v>
+        <v>0.5213849688416867</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5021459227467812</v>
+        <v>0.5095384447515822</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5010729613733905</v>
+        <v>0.5102446594408477</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5</v>
+        <v>0.5302217453505007</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5</v>
+        <v>0.5554317911786814</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.5526342111006037</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5010729613733905</v>
+        <v>0.5348030479377319</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5007198540287577</v>
+        <v>0.5288002230789748</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.5448112921607139</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.5241689095802721</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.5937931912417255</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.6157297955917655</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.6131777236245484</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.5607617419558206</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5607617419558206</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5568502824858756</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5568502824858756</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.504528260711428</v>
       </c>
     </row>
   </sheetData>
